--- a/SWACS.xlsx
+++ b/SWACS.xlsx
@@ -16,49 +16,58 @@
     <t/>
   </si>
   <si>
+    <t>20072581</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED ORG 20G</t>
+  </si>
+  <si>
+    <t>SWACS</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20038042</t>
   </si>
   <si>
     <t>TOLL MILK CANDY 120</t>
   </si>
   <si>
-    <t>SWACS</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>20115472</t>
@@ -68,15 +77,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -514,50 +514,50 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -594,10 +594,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -614,10 +614,10 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
